--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260901.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260901.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>178,241,000</t>
+          <t>179,141,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.57%</t>
+          <t>9.55%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>917,237,000</t>
+          <t>919,737,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.42%</t>
+          <t>9.54%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>373,140,486</t>
+          <t>375,940,486</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.54%</t>
+          <t>6.51%</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>39,110,000</t>
+          <t>39,360,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>4.05%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>188,701,000</t>
+          <t>190,201,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.80%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.44%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>27,429,000</t>
+          <t>27,629,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>64,642,000</t>
+          <t>64,742,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>453,196,250</t>
+          <t>451,396,250</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -880,51 +880,51 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>356,220,964</t>
+          <t>32,456,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>32,006,000</t>
+          <t>355,020,964</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
@@ -941,73 +941,73 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>26,529,000</t>
+          <t>26,729,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>234,008,056</t>
+          <t>29,461,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>131,081,000</t>
+          <t>233,408,056</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>197,661,000</t>
+          <t>84,290,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1029,78 +1029,78 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>99,498,442</t>
+          <t>99,598,442</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>84,040,000</t>
+          <t>131,081,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>145,204,000</t>
+          <t>197,061,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>29,401,000</t>
+          <t>145,204,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>35,510,000</t>
+          <t>35,605,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -1161,56 +1161,56 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>190,203,000</t>
+          <t>190,453,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>53,888,000</t>
+          <t>272,189,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>272,189,000</t>
+          <t>53,588,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>256,199,845</t>
+          <t>255,099,845</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>90,030,061</t>
+          <t>89,780,061</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>4,186,000</t>
+          <t>1,986,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1319,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>B95552</t>
+          <t>B95553</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>P08凱控1A</t>
+          <t>P08凱控1B</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>85,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
@@ -1337,17 +1337,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>B95553</t>
+          <t>B95555</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>P08凱控1B</t>
+          <t>P09凱控1B</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>185,000,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr"/>
@@ -1355,17 +1355,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>B95555</t>
+          <t>B96525</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>P09凱控1B</t>
+          <t>P11元金2</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>120,000,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr"/>
@@ -1373,17 +1373,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>B96525</t>
+          <t>B97872</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>P11元金2</t>
+          <t>P13富邦金1</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>120,000,000</t>
+          <t>45,000,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -1391,17 +1391,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>B97872</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>P13富邦金1</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>45,000,000</t>
+          <t>31,076,203,859</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr"/>
@@ -1409,17 +1409,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>31,086,695,777</t>
+          <t>5,591,475,826</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr"/>
@@ -1427,38 +1427,20 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>PFUR_NTD</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>5,110,933,426</t>
+          <t>-134,132,350</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>PFUR_NTD</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>-49,471,279</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
